--- a/www/download/IND.surplus_value.empe_ms.r.pc.zdW13.xlsx
+++ b/www/download/IND.surplus_value.empe_ms.r.pc.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>0.763169179824134</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>0.73081908387013</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.56</t>
+          <t>0.815560866054604</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>0.807043205007665</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>73.98</t>
+          <t>0.739838918999985</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>0.828871604546963</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>0.87940979258422</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>81.49</t>
+          <t>0.814927287914331</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>71.99</t>
+          <t>0.719932038704327</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505873697168595</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>0.444445016264482</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>0.477564050745577</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>44.53</t>
+          <t>0.445251365671529</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>0.586587748768102</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>65.69</t>
+          <t>0.65689142429434</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>0.244670168501123</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.300395816587684</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>0.533387347244367</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>0.505608983301783</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>0.498587974559127</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>0.569424056741179</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>0.538568618942151</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>53.64</t>
+          <t>0.536351005858883</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>45.51</t>
+          <t>0.455127011393974</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>0.379388329808287</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>0.350245209589995</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>0.321121548919257</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>0.310389393763545</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>0.2765879392835</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>0.375099058728453</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.0421346549556707</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-0.0665928306037979</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.0208982490236137</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.0147044107913741</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.58</t>
+          <t>-0.0958170694386415</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.45</t>
+          <t>-0.12445429792704</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-17.6</t>
+          <t>-0.176012476084763</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-0.238811299818695</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-35.98</t>
+          <t>-0.359781442308209</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>-0.406401755715968</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-39.37</t>
+          <t>-0.393682411528769</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-38.31</t>
+          <t>-0.383100884802501</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-35.82</t>
+          <t>-0.358183829199079</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-28.8</t>
+          <t>-0.287953334365282</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-32.9</t>
+          <t>-0.328991774283665</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>277.27</t>
+          <t>2.77271716672977</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>333.22</t>
+          <t>3.33216571636054</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>392.64</t>
+          <t>3.92640171089035</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>269.68</t>
+          <t>2.69678656530257</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>303.52</t>
+          <t>3.03520572644091</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>311.8</t>
+          <t>3.11795617098477</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>298.63</t>
+          <t>2.98629493787331</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>314.19</t>
+          <t>3.14190760520639</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>465.6</t>
+          <t>4.65595222503249</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>3.21997566011351</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>339.95</t>
+          <t>3.39946013316828</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>355.87</t>
+          <t>3.55868056770798</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>353.54</t>
+          <t>3.53542265340509</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>318.5</t>
+          <t>3.1849853632524</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>283.21</t>
+          <t>2.83210436652448</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>143.4</t>
+          <t>1.43402528854517</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>155.95</t>
+          <t>1.55954341096544</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>180.74</t>
+          <t>1.80737964179074</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>189.07</t>
+          <t>1.89069193477981</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>228.02</t>
+          <t>2.28021750331333</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>257.68</t>
+          <t>2.57684600920561</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>287.75</t>
+          <t>2.8774518974873</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>317.94</t>
+          <t>3.17939818284774</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>337.27</t>
+          <t>3.3726731749876</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>339.42</t>
+          <t>3.39424984265247</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>330.47</t>
+          <t>3.30465368703286</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>338.95</t>
+          <t>3.38953663638082</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>348.67</t>
+          <t>3.48670513261448</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>343.31</t>
+          <t>3.43312627301661</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>360.65</t>
+          <t>3.60653861788299</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>120.11</t>
+          <t>1.20111380380796</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>132.93</t>
+          <t>1.32925409927223</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>151.47</t>
+          <t>1.51466954788623</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>1.34703642630028</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>125.23</t>
+          <t>1.2523376813654</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>106.52</t>
+          <t>1.06519753139934</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>0.948543218267695</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>95.44</t>
+          <t>0.954423794400316</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>0.823127299154404</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>0.763642168768134</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>63.52</t>
+          <t>0.635161580344293</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>0.58517600248866</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>65.52</t>
+          <t>0.655222141468231</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>67.09</t>
+          <t>0.67091811194675</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>0.818340160987504</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>-0.317006684540492</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-27.83</t>
+          <t>-0.278312178212826</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-27.83</t>
+          <t>-0.278303232240926</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-0.274286064293841</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-26.42</t>
+          <t>-0.264195499555162</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-0.236664771115092</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-16.2</t>
+          <t>-0.161973854977886</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-0.114139150773344</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-0.0444269707612603</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>0.0537996814959574</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>0.12132563598402</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>0.154493355642089</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>0.312253250309361</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>0.351464916203806</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>0.401391300657795</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>141.85</t>
+          <t>1.41854890287996</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>134.95</t>
+          <t>1.34951879631473</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>168.89</t>
+          <t>1.68889000016391</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>156.9</t>
+          <t>1.56899965407052</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>1.39002305294459</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>144.46</t>
+          <t>1.44463282455553</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>119.6</t>
+          <t>1.19598459907497</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>116.75</t>
+          <t>1.16748132523514</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>97.84</t>
+          <t>0.978357426070121</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>102.05</t>
+          <t>1.02046847916777</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>103.85</t>
+          <t>1.0385207694644</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>112.58</t>
+          <t>1.12582089100362</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>138.59</t>
+          <t>1.38589778318367</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>104.6</t>
+          <t>1.04595472254225</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>144.35</t>
+          <t>1.44353393571881</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>460.27</t>
+          <t>4.60267458102713</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>297.38</t>
+          <t>2.97375022284967</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>338.54</t>
+          <t>3.38539781006387</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>321.83</t>
+          <t>3.21831763896239</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>324.74</t>
+          <t>3.24738564974302</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>340.27</t>
+          <t>3.40267787561567</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>305.83</t>
+          <t>3.05825502300437</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>292.59</t>
+          <t>2.92592812465366</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>254.93</t>
+          <t>2.54926279614415</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>230.94</t>
+          <t>2.30940597564375</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>220.91</t>
+          <t>2.20908593635494</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>233.88</t>
+          <t>2.33880301626224</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>227.72</t>
+          <t>2.27718509304788</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>213.69</t>
+          <t>2.13692024753459</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>2.62303727658443</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.102606664869386</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>0.216136839848883</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>0.391812726716821</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>0.365216115699567</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>0.316483493940632</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>0.244010468311939</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>0.273918328712936</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>0.298448745635467</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>0.135939169003017</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>0.103615585132649</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>0.152172573017543</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>0.161126251490077</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>0.148477794560005</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.158416121889</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>0.204628269019782</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-0.0280417041817045</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.00224996093935903</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>0.389903377696786</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>0.222765149652315</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.211047774164994</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0.269960884617884</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>0.219238103376615</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>0.177831611144105</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.00865954372548972</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.00597228213087941</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.00438952784981139</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.0110707604534952</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.00640342865819987</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.0267473296019209</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>0.141336372243123</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>0.7421290905911</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>0.869318961609123</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>123.88</t>
+          <t>1.23883123871656</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>106.07</t>
+          <t>1.06067733744567</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>96.58</t>
+          <t>0.965845394715297</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>101.2</t>
+          <t>1.01200313391842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90.87</t>
+          <t>0.908727417590849</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>83.56</t>
+          <t>0.835573571425327</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>0.799040912278214</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>59.37</t>
+          <t>0.593693935648543</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>0.57948813760341</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>0.541765273365953</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>0.574718584047748</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>54.77</t>
+          <t>0.547678784976779</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0.732124810244503</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>444.09</t>
+          <t>4.4408744203443</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>395.82</t>
+          <t>3.95824963132961</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>372.93</t>
+          <t>3.72926709541491</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>343.13</t>
+          <t>3.43130350876432</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>366.42</t>
+          <t>3.66418299079686</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>302.29</t>
+          <t>3.02291142173632</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>291.59</t>
+          <t>2.91590489460936</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>213.35</t>
+          <t>2.13346480083312</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>164.44</t>
+          <t>1.64440872687412</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>156.37</t>
+          <t>1.56372673389837</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>181.41</t>
+          <t>1.81410790764877</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>187.8</t>
+          <t>1.87798305505574</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>166.03</t>
+          <t>1.66028532975448</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>140.97</t>
+          <t>1.40968863707741</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>152.14</t>
+          <t>1.52144023896739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>0.716506458199736</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64.53</t>
+          <t>0.645263595817647</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>0.96315088583028</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>83.31</t>
+          <t>0.833097873045817</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>83.43</t>
+          <t>0.834288668137813</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>102.79</t>
+          <t>1.02790399860825</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>96.51</t>
+          <t>0.965122255827138</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>94.45</t>
+          <t>0.944458454578103</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>73.83</t>
+          <t>0.738319968736407</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>68.61</t>
+          <t>0.686073493068291</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>0.660034695302629</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>61.59</t>
+          <t>0.615867158307859</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>65.13</t>
+          <t>0.651304784282917</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>0.608671670416352</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>71.16</t>
+          <t>0.711597312945646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>0.544339729143708</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>0.564087080754788</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.07</t>
+          <t>0.800719218082521</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>63.78</t>
+          <t>0.637787836971288</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>0.536903367949521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.536494975540045</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>0.458597190007204</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>0.382382800237839</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>0.304796703921712</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>0.222562188871441</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>0.217074538460241</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>0.233656352294352</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>0.261099725236298</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>0.253719736555373</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>0.364967516013228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>0.879514102090244</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>0.893554156568226</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>105.3</t>
+          <t>1.05295424401943</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>0.898294010625201</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>79.81</t>
+          <t>0.79812509044933</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>73.53</t>
+          <t>0.735279678130283</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>64.37</t>
+          <t>0.6437310689827</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>60.31</t>
+          <t>0.60306188111551</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.496014814210292</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>0.406812349156852</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>0.419415846458699</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>0.408227760754325</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>0.451056114388238</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>0.60474181424383</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.71542419422688</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>222.31</t>
+          <t>2.22312834404788</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>201.98</t>
+          <t>2.01978714384381</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>207.51</t>
+          <t>2.07513431190446</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>210.21</t>
+          <t>2.10210437212259</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>185.06</t>
+          <t>1.85059054700941</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>167.28</t>
+          <t>1.67283448624524</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>185.86</t>
+          <t>1.85859124318531</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>155.05</t>
+          <t>1.5505145705069</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>162.87</t>
+          <t>1.62870260857534</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>154.31</t>
+          <t>1.54313990621995</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>160.39</t>
+          <t>1.60392383050544</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>156.98</t>
+          <t>1.56977042055207</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>141.33</t>
+          <t>1.41326400543679</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>143.63</t>
+          <t>1.43625316696692</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>139.06</t>
+          <t>1.39058427005476</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>249.06</t>
+          <t>2.49061366364137</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>258.34</t>
+          <t>2.58336705359432</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>2.81995998690824</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>290.34</t>
+          <t>2.90340934159185</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>301.62</t>
+          <t>3.01621400859273</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>288.78</t>
+          <t>2.88776419144882</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>307.6</t>
+          <t>3.07604594359725</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>282.52</t>
+          <t>2.82520576710834</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>270.75</t>
+          <t>2.70752769017099</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>323.19</t>
+          <t>3.23194523002825</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>336.15</t>
+          <t>3.36145109841688</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>357.83</t>
+          <t>3.57827181129073</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>346.02</t>
+          <t>3.46017922350214</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>346.23</t>
+          <t>3.46234150655341</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>383.04</t>
+          <t>3.83036348975067</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>0.735801905971119</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>92.83</t>
+          <t>0.928284216037986</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>109.94</t>
+          <t>1.09942861349083</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>138.22</t>
+          <t>1.38224821946744</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>153.54</t>
+          <t>1.53538581455004</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>137.09</t>
+          <t>1.37086680569977</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>121.05</t>
+          <t>1.21052925251234</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>106.43</t>
+          <t>1.06434830021066</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>95.12</t>
+          <t>0.951212251084375</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>0.844996268722092</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>0.872000699009705</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>96.79</t>
+          <t>0.967892918811499</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>0.887430422854543</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>0.937288005330592</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>0.935998221540183</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>0.0361455884946891</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>0.147284293527079</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>0.103600401990743</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>0.118582101930179</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>0.155211822547086</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>0.213815116349347</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>0.25273432169434</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>0.335151984172855</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>0.320969243675349</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>0.306131234796279</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>0.267571417628959</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>0.231495094806625</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>27.57</t>
+          <t>0.275674453493246</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>32.77</t>
+          <t>0.327691551365662</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>0.282760308376414</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>0.863914089105507</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>0.817542593576147</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>108.92</t>
+          <t>1.08924063671712</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>117.26</t>
+          <t>1.17256984347943</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>117.51</t>
+          <t>1.17505435565249</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>112.34</t>
+          <t>1.12340312135967</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>0.913854958842748</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>0.807731387612977</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>1.03797679764378</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>116.22</t>
+          <t>1.16223127123134</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>106.91</t>
+          <t>1.06906177913074</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>115.95</t>
+          <t>1.15948694628382</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>105.46</t>
+          <t>1.054627830467</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>0.818351067228072</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>0.642720771888744</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>0.728787079878464</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.76760110323946</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>0.927782933057681</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>91.79</t>
+          <t>0.917865474668624</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>0.920043686129911</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>95.53</t>
+          <t>0.955337543270001</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>0.785725466258767</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>0.715954942960415</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>0.688062492227756</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.450007280790621</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.43334950111676</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>40.28</t>
+          <t>0.40276052831184</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>0.469604044113352</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>50.82</t>
+          <t>0.508159677367337</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>0.666329073816806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.584139553038437</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>80.76</t>
+          <t>0.807609714288258</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>102.63</t>
+          <t>1.02630126741478</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>109.54</t>
+          <t>1.09536130533619</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>97.75</t>
+          <t>0.977451768573731</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>0.871813062274177</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>90.69</t>
+          <t>0.90685330995146</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>102.09</t>
+          <t>1.02093259506924</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>96.11</t>
+          <t>0.9611013259696</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>86.86</t>
+          <t>0.868553517787687</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85.67</t>
+          <t>0.85670497545089</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>0.950098896421816</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>115.62</t>
+          <t>1.15618061810879</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>122.37</t>
+          <t>1.22368958306796</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>115.66</t>
+          <t>1.1566049826499</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>1.23960204550453</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>130.01</t>
+          <t>1.30008585507453</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>155.23</t>
+          <t>1.55231903614016</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>182.35</t>
+          <t>1.82345565324156</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>195.1</t>
+          <t>1.95101372266745</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>181.21</t>
+          <t>1.81207104143235</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>188.7</t>
+          <t>1.88701185760568</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>179.87</t>
+          <t>1.79873559013151</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>160.09</t>
+          <t>1.60085650642654</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>159.09</t>
+          <t>1.59088857542379</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>161.97</t>
+          <t>1.61974154699652</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>153.71</t>
+          <t>1.53708444574127</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>157.47</t>
+          <t>1.57470057697176</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>179.44</t>
+          <t>1.79444656196458</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>197.28</t>
+          <t>1.97280582506625</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>348.83</t>
+          <t>3.48828822280141</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>322.84</t>
+          <t>3.22840787512189</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>328.37</t>
+          <t>3.28371127379246</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>266.98</t>
+          <t>2.66979135618004</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>253.96</t>
+          <t>2.53960382783567</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>249.51</t>
+          <t>2.49513979280171</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>250.82</t>
+          <t>2.50815727999988</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>243.48</t>
+          <t>2.4347870808855</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>204.01</t>
+          <t>2.04007192735548</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>259.64</t>
+          <t>2.59636682747891</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>255.66</t>
+          <t>2.55663741023707</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>245.32</t>
+          <t>2.45318296452318</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>260.77</t>
+          <t>2.6076510411879</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>239.17</t>
+          <t>2.39165540097397</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>259.47</t>
+          <t>2.59473843571827</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>0.110237924475187</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>0.301280169597021</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>0.583811576678473</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.73</t>
+          <t>0.657285324550135</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63.01</t>
+          <t>0.630101352487139</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>61.22</t>
+          <t>0.612213115146536</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>0.773191123398121</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>0.660212983863334</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>0.679872932936094</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>0.638295715302242</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>0.603174937800406</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>0.622483386724012</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>0.887272870424695</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>0.636000659923079</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>101.45</t>
+          <t>1.01445995327159</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>388.01</t>
+          <t>3.88013834174535</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>341.12</t>
+          <t>3.41119888710248</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>348.53</t>
+          <t>3.48534463441708</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>351.33</t>
+          <t>3.51332607022299</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>362.3</t>
+          <t>3.62302355645457</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>433.92</t>
+          <t>4.33915668111665</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>436.29</t>
+          <t>4.36285227268519</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>455.62</t>
+          <t>4.55620181872486</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>417.47</t>
+          <t>4.17473804444656</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>428.97</t>
+          <t>4.28965591443882</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>401.09</t>
+          <t>4.01091226297486</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>364.45</t>
+          <t>3.64453632745496</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>311.91</t>
+          <t>3.11914829722955</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>280.35</t>
+          <t>2.80345172734491</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>354.18</t>
+          <t>3.5417986114702</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>247.99</t>
+          <t>2.47985384758304</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>266.28</t>
+          <t>2.66281024907367</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>304.93</t>
+          <t>3.04926860445742</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>281.56</t>
+          <t>2.81557161275489</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>265.45</t>
+          <t>2.65451853389332</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>259.21</t>
+          <t>2.59209145533124</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>228.88</t>
+          <t>2.2888463929339</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>232.35</t>
+          <t>2.32350127492205</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>237.59</t>
+          <t>2.37593141575461</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>259.31</t>
+          <t>2.59310515537785</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>265.97</t>
+          <t>2.65969194763279</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>293.4</t>
+          <t>2.9339981842923</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>306.72</t>
+          <t>3.06717588328979</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>311.89</t>
+          <t>3.11894330473204</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>318.12</t>
+          <t>3.18124555438363</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>151.66</t>
+          <t>1.51658666400112</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>135.77</t>
+          <t>1.35766345776185</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>186.92</t>
+          <t>1.86918972301438</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>164.33</t>
+          <t>1.64325735546975</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>133.51</t>
+          <t>1.33513140585731</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>118.6</t>
+          <t>1.18599414772408</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>63.59</t>
+          <t>0.63589659994795</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>0.8187678668072</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>113.04</t>
+          <t>1.13037447394538</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>112.12</t>
+          <t>1.12115813274402</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>113.34</t>
+          <t>1.13343131670329</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>124.41</t>
+          <t>1.24410409659709</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>114.79</t>
+          <t>1.14794200488249</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>99.38</t>
+          <t>0.993775793266264</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>128.26</t>
+          <t>1.28263859417392</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>-0.181469360874333</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-14.21</t>
+          <t>-0.142125230671583</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>0.298246897277495</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>0.0544205703705907</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.0193649607181758</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>0.0513554615807916</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-0.0545414561364813</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>-0.147397425653982</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-0.083218050717524</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>-0.0966806795692945</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-0.0603545019214039</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-0.0659497846649715</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-7.99</t>
+          <t>-0.0798644025986984</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-0.133713183943075</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-0.100323136825815</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>113.4</t>
+          <t>1.13395604984538</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>101.75</t>
+          <t>1.01749676800838</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>101.03</t>
+          <t>1.01026986700033</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>95.18</t>
+          <t>0.951751668147267</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>1.1130263600839</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>124.09</t>
+          <t>1.24094258457767</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>195.19</t>
+          <t>1.95194762483423</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>207.47</t>
+          <t>2.07473143425546</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>225.8</t>
+          <t>2.25796356108735</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>253.71</t>
+          <t>2.53711181724137</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>244.96</t>
+          <t>2.44956131634127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>256.63</t>
+          <t>2.56626546891566</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>265.09</t>
+          <t>2.65093976969436</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>226.05</t>
+          <t>2.26052646217622</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>260.16</t>
+          <t>2.60163147034233</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>76.31</t>
+          <t>0.763119994528955</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>73.31</t>
+          <t>0.7331193818629</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>0.983261759214528</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>0.787035992664562</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>0.859703500331139</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>85.41</t>
+          <t>0.854138926609076</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>77.06</t>
+          <t>0.770567003770702</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>82.34</t>
+          <t>0.823425712283976</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>142.08</t>
+          <t>1.42077307978116</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>0.878929157990235</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>0.923556640995898</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>118.16</t>
+          <t>1.1816136969314</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>124.36</t>
+          <t>1.24356177119832</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>115.84</t>
+          <t>1.15838020646067</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>144.75</t>
+          <t>1.44752947517515</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>1.18697514195576</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>130.06</t>
+          <t>1.30057363023718</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>1.45997847089506</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>103.59</t>
+          <t>1.03585196307989</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>0.93861192006783</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>65.74</t>
+          <t>0.657404153047789</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>64.78</t>
+          <t>0.64775612514631</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>130.26</t>
+          <t>1.30259958989587</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>217.71</t>
+          <t>2.17706393965681</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>174.74</t>
+          <t>1.74738231689766</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>145.01</t>
+          <t>1.45012311463585</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>155.02</t>
+          <t>1.55017866595691</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>142.49</t>
+          <t>1.42490880379431</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>129.06</t>
+          <t>1.29063279760318</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>158.26</t>
+          <t>1.5826311117386</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>137.32</t>
+          <t>1.37319122735009</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>126.46</t>
+          <t>1.26462557101829</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>149.62</t>
+          <t>1.49618384932125</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>166.02</t>
+          <t>1.66024815263531</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>175.87</t>
+          <t>1.75866418612027</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1.48003761331176</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>159.49</t>
+          <t>1.59494903145265</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>155.25</t>
+          <t>1.55245571665183</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>136.1</t>
+          <t>1.36095319699202</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>128.43</t>
+          <t>1.28427027310331</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>124.36</t>
+          <t>1.24357110301694</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>127.31</t>
+          <t>1.27306461234362</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>106.79</t>
+          <t>1.06789723179386</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>0.807038099490379</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>0.806618083134415</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>503.24</t>
+          <t>5.03239047145891</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>478.21</t>
+          <t>4.78212801268762</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>493.21</t>
+          <t>4.93205824343532</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>487.73</t>
+          <t>4.87727942155094</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>529.2</t>
+          <t>5.29203540387657</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>508.58</t>
+          <t>5.08577602593214</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>492.01</t>
+          <t>4.92011689831085</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>475.78</t>
+          <t>4.75779406516848</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>406.95</t>
+          <t>4.06950331677956</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>316.09</t>
+          <t>3.16087556603054</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>331.67</t>
+          <t>3.31674996741454</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>303.76</t>
+          <t>3.03761836251677</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>236.91</t>
+          <t>2.36906151351053</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>246.64</t>
+          <t>2.46642965444069</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>186.78</t>
+          <t>1.86776843733893</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>0.869134621523698</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>0.927785972400904</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>117.23</t>
+          <t>1.17230223063686</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>106.26</t>
+          <t>1.06256418145084</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>1.06816075607121</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>112.49</t>
+          <t>1.12493392836179</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100.48</t>
+          <t>1.00481921801889</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>101.81</t>
+          <t>1.01805830763422</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>84.61</t>
+          <t>0.84611556480919</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>96.75</t>
+          <t>0.967450964332257</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>107.17</t>
+          <t>1.07171140233158</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>106.99</t>
+          <t>1.06987905487219</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>113.35</t>
+          <t>1.13345719930627</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>0.522803084435268</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>0.560415463134497</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>0.534130262087749</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>0.501502362508258</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>0.750397767886262</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>0.614022042086069</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>0.61837395403857</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>0.489567190549182</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>0.471987624469414</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.421056791351303</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>0.317604061340813</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>0.274612236835753</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>0.240250586681191</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245259608994791</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>0.216213550054105</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>0.308629351432486</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>48.12</t>
+          <t>0.481177661530796</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>169.12</t>
+          <t>1.69116603264239</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>143.75</t>
+          <t>1.43747374995194</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>141.81</t>
+          <t>1.41807554573221</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>142.4</t>
+          <t>1.42399054127237</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>123.29</t>
+          <t>1.2328822773528</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>170.29</t>
+          <t>1.70294995777053</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>192.53</t>
+          <t>1.92529456541241</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>247.71</t>
+          <t>2.47707660581347</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>243.25</t>
+          <t>2.43249770684569</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>215.41</t>
+          <t>2.15407389967771</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>239.78</t>
+          <t>2.39778346593467</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>258.59</t>
+          <t>2.5858977785417</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>256.72</t>
+          <t>2.56721805815638</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>103.68</t>
+          <t>1.03682213443569</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>131.07</t>
+          <t>1.31074709433347</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>85.16</t>
+          <t>0.85157772632772</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>0.739151430653626</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>0.987962734662101</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>1.08327697030698</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>116.2</t>
+          <t>1.16195265301844</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>106.96</t>
+          <t>1.06955897072653</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>1.02278147386659</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>108.84</t>
+          <t>1.08843673759956</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>108.03</t>
+          <t>1.08028729041626</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>112.05</t>
+          <t>1.1204903959075</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>1.15499138263128</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>125.13</t>
+          <t>1.25134756944013</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>152.43</t>
+          <t>1.52434571220856</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>154.73</t>
+          <t>1.5472597859504</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>183.75</t>
+          <t>1.83749397184274</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>127.38</t>
+          <t>1.27375814200347</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>132.24</t>
+          <t>1.3224404028337</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>135.14</t>
+          <t>1.35142273218608</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>122.31</t>
+          <t>1.22312342598981</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>114.4</t>
+          <t>1.14403949199146</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>99.22</t>
+          <t>0.992150367608615</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>0.911027870165757</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>0.843765615631183</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>78.28</t>
+          <t>0.782799331215719</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>77.05</t>
+          <t>0.77051197757954</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>76.62</t>
+          <t>0.766194933549996</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>83.77</t>
+          <t>0.837743073843874</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>0.958420258214401</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>109.41</t>
+          <t>1.09405899771706</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>116.49</t>
+          <t>1.1648723037455</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.0127987350070456</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>0.0594430859371158</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>0.0643526177232556</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.0613626085826744</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>0.0602976204637673</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>0.0483124482342006</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0.0595764049972289</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0.0800131939530786</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>0.15594300398153</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>0.225056485363291</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222298651750885</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>0.227249422941632</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>0.33409627720114</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>0.36556176417692</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>0.416312911983843</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>0.236933924843975</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>0.299879179305991</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>0.322803888710872</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>0.315387592858243</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>0.315465325290877</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304533768374642</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>0.32123357129148</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>0.343283444926916</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>0.374032045637155</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>0.416494423627585</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>0.426579650375296</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>44.57</t>
+          <t>0.445671776975347</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>54.21</t>
+          <t>0.542111796026789</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>56.64</t>
+          <t>0.566404454225899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>0.603402216422627</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
